--- a/stim/stim_list_no_learning_familiarization.xlsx
+++ b/stim/stim_list_no_learning_familiarization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\docs\code\matlab\Task_SpeechMotorSequenceLearning\stim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F4AADB-4743-4C74-B493-28EC5E5FEFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268E2191-AB0C-4BF9-AD00-7379709E988C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4170" yWindow="2520" windowWidth="21600" windowHeight="11385" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="8">
   <si>
     <t>group1</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>non-native</t>
+  </si>
+  <si>
+    <t>STOP (non-native)</t>
   </si>
 </sst>
 </file>
@@ -405,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="3"/>
@@ -444,13 +447,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -458,13 +461,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -472,41 +475,41 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -514,13 +517,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -528,27 +531,27 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -556,44 +559,156 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
         <v>24</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>73</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="1">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="1">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0</v>
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>75</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/stim/stim_list_no_learning_familiarization.xlsx
+++ b/stim/stim_list_no_learning_familiarization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\docs\code\matlab\Task_SpeechMotorSequenceLearning\stim\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Task\Task_SpeechMotorSequenceLearning\stim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268E2191-AB0C-4BF9-AD00-7379709E988C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AEA9E0-DF48-4276-8701-36C2F7F3BE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -610,7 +610,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -638,7 +638,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
